--- a/public/豆知識/豆知識①.xlsx
+++ b/public/豆知識/豆知識①.xlsx
@@ -855,7 +855,7 @@
         <v>103</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>済</v>
       </c>
     </row>
     <row r="28">
